--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 бррсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 бррсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF77723-201C-4BD2-B7BE-030158C26593}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8E29E3-DBFD-4D47-98DD-366BA5670B12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -151,6 +148,12 @@
   </si>
   <si>
     <t>матрица</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>18,07,</t>
   </si>
 </sst>
 </file>
@@ -751,25 +754,25 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -814,19 +817,21 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
+      <c r="Q4" s="1" t="s">
+        <v>41</v>
       </c>
-      <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -900,7 +905,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>708.40000000000009</v>
+        <v>700</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -915,7 +920,7 @@
       <c r="V5" s="1"/>
       <c r="W5" s="4">
         <f>SUM(W6:W500)</f>
-        <v>228.96999999999997</v>
+        <v>226.5</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -946,10 +951,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>224</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -995,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W6" s="1">
         <f t="shared" ref="W6:W16" si="2">G6*Q6</f>
@@ -1030,10 +1035,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1">
         <v>90.763999999999996</v>
@@ -1052,7 +1057,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1085,7 +1090,7 @@
         <v>0.91959999999999997</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
@@ -1120,10 +1125,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1">
         <v>261.73200000000003</v>
@@ -1142,7 +1147,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1175,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" si="2"/>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>130</v>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1263,7 +1268,7 @@
         <v>1.4</v>
       </c>
       <c r="V9" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="2"/>
@@ -1298,10 +1303,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>-11</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1340,12 +1345,11 @@
         <v>21.6</v>
       </c>
       <c r="Q10" s="5">
-        <f>14*P10-O10-F10</f>
-        <v>225.40000000000003</v>
+        <v>220</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13.749999999999998</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="5"/>
@@ -1360,7 +1364,7 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1">
         <f t="shared" si="2"/>
-        <v>67.62</v>
+        <v>66</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -1391,10 +1395,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1413,7 +1417,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1433,12 +1437,11 @@
         <v>15.2</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q11:Q12" si="6">15*P11-O11-F11</f>
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.736842105263159</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
@@ -1453,7 +1456,7 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1">
         <f t="shared" si="2"/>
-        <v>46.199999999999996</v>
+        <v>45</v>
       </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -1484,10 +1487,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
@@ -1506,7 +1509,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1526,12 +1529,11 @@
         <v>25.4</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="6"/>
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.960629921259843</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="5"/>
@@ -1546,7 +1548,7 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1">
         <f t="shared" si="2"/>
-        <v>52.849999999999994</v>
+        <v>52.5</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -1577,10 +1579,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1">
         <v>-6</v>
@@ -1599,7 +1601,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1634,7 +1636,7 @@
         <v>18</v>
       </c>
       <c r="V13" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" si="2"/>
@@ -1669,10 +1671,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
         <v>-9</v>
@@ -1691,7 +1693,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1709,12 +1711,11 @@
         <v>17.600000000000001</v>
       </c>
       <c r="Q14" s="5">
-        <f>10*P14-O14-F14</f>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>10.113636363636363</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
@@ -1729,7 +1730,7 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1">
         <f t="shared" si="2"/>
-        <v>62.3</v>
+        <v>62.999999999999993</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -1760,10 +1761,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1">
         <v>115</v>
@@ -1778,7 +1779,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1809,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="2"/>
@@ -1844,10 +1845,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1">
         <v>17</v>
@@ -1866,7 +1867,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1899,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" si="2"/>
